--- a/Chapter-6b/7 - OT - Checklist for CSSD Equipment and Wattage.xlsx
+++ b/Chapter-6b/7 - OT - Checklist for CSSD Equipment and Wattage.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\Architecture Manual\3 - Final Version - Under Review\Section 6b - Operation theatre &amp; sterilisation process\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sasipriyakarumanchi/Library/CloudStorage/GoogleDrive-sashi@aravind.org/My Drive/Architecture Manual/3 - Final Version - Under Review/Section 6b - Operation theatre &amp; sterilisation process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3DF647-4B1F-4D42-AD76-8BDBA4E70C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F2AE1C-ED19-D84D-80DF-55D41B0FE721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FC6FB089-B3AA-49DB-9C09-AD50FCBA7E4D}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{FC6FB089-B3AA-49DB-9C09-AD50FCBA7E4D}"/>
   </bookViews>
   <sheets>
     <sheet name="Central Sterilisation " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Central Sterilisation '!$A$1:$N$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Central Sterilisation '!$A$1:$N$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
-  <si>
-    <t>Standardised Architectural Modules</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
   <si>
     <t>Supply</t>
   </si>
@@ -176,21 +173,6 @@
   </si>
   <si>
     <t xml:space="preserve">The list given below is only indicative; please make changes to (a) size/capacity of the equiment listed here; (b) include additional equipment required; c) power supply requirements; </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Section 5b: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Century Gothic"/>
-        <family val="2"/>
-      </rPr>
-      <t>Guidelines for OT and Ward</t>
-    </r>
   </si>
   <si>
     <r>
@@ -217,9 +199,6 @@
     </r>
   </si>
   <si>
-    <t>Version : 1 - Oct-14</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Others </t>
     </r>
@@ -240,12 +219,15 @@
   <si>
     <t>Air supply pipes - inlet for fresh air &amp; outlet</t>
   </si>
+  <si>
+    <t>Standardised Architectural Modules for Layouts</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,13 +252,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="4"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -755,155 +730,155 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -928,7 +903,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="184731" cy="264560"/>
@@ -983,9 +958,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1023,7 +998,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1129,7 +1104,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1271,7 +1246,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1279,547 +1254,526 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B99356-3A13-4A5B-B877-949AAE300F6A}">
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.6796875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="27.40625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.40625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="2" style="3" customWidth="1"/>
-    <col min="5" max="5" width="4.76953125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="14.58984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.31640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.40625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.08984375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.83203125" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.40625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.04296875" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.81640625" style="3"/>
+    <col min="13" max="13" width="13.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+    </row>
+    <row r="2" spans="1:14" ht="10.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+    </row>
+    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+    </row>
+    <row r="4" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+    </row>
+    <row r="5" spans="1:14" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+    </row>
+    <row r="6" spans="1:14" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+    </row>
+    <row r="7" spans="1:14" s="10" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="36"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="40"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-    </row>
-    <row r="2" spans="1:14" ht="10.5" hidden="1" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-    </row>
-    <row r="3" spans="1:14" ht="17.75" x14ac:dyDescent="0.75">
-      <c r="A3" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-    </row>
-    <row r="4" spans="1:14" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="41" t="s">
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-    </row>
-    <row r="5" spans="1:14" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A5" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-    </row>
-    <row r="6" spans="1:14" ht="28.9" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-    </row>
-    <row r="7" spans="1:14" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-    </row>
-    <row r="8" spans="1:14" s="10" customFormat="1" ht="17.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.75">
-      <c r="A8" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="56" t="s">
+    </row>
+    <row r="8" spans="1:14" s="10" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="47"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="D8" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="43"/>
+      <c r="G8" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="43"/>
+      <c r="N8" s="45"/>
+    </row>
+    <row r="9" spans="1:14" s="56" customFormat="1" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="45" t="s">
+      <c r="B9" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="55"/>
+    </row>
+    <row r="10" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="13">
         <v>1</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="49" t="s">
+      <c r="B10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N8" s="51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="10" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A9" s="54"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="31" t="s">
+      <c r="C10" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="M9" s="50"/>
-      <c r="N9" s="52"/>
-    </row>
-    <row r="10" spans="1:14" s="11" customFormat="1" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.75">
-      <c r="A10" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="35"/>
-    </row>
-    <row r="11" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A11" s="15">
-        <v>1</v>
+      <c r="E10" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="22.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
+        <v>2</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N11" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A12" s="15">
-        <v>2</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>19</v>
+    </row>
+    <row r="12" spans="1:14" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13">
+        <v>3</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="C12" s="7">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="6">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N12" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A13" s="15">
+      <c r="M12" s="2"/>
+      <c r="N12" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="56" customFormat="1" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="59"/>
+      <c r="N13" s="60"/>
+    </row>
+    <row r="14" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>1</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="11" customFormat="1" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A14" s="14" t="s">
+      <c r="E14" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="14"/>
+    </row>
+    <row r="15" spans="1:14" s="56" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B15" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="38"/>
-    </row>
-    <row r="15" spans="1:14" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A15" s="15">
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="59"/>
+      <c r="M15" s="59"/>
+      <c r="N15" s="60"/>
+    </row>
+    <row r="16" spans="1:14" ht="25.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
         <v>1</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="16"/>
-    </row>
-    <row r="16" spans="1:14" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37" t="s">
+      <c r="B16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="38"/>
-    </row>
-    <row r="17" spans="1:14" ht="25.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A17" s="15">
-        <v>1</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="C16" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="G16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>2</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="C17" s="7">
-        <v>1.05</v>
+        <v>0.65</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="6">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="59" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A18" s="15">
-        <v>2</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.65</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="N17" s="33"/>
+    </row>
+    <row r="18" spans="1:14" s="56" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="60"/>
+    </row>
+    <row r="19" spans="1:14" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>1</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="60"/>
-    </row>
-    <row r="19" spans="1:14" s="11" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A19" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="38"/>
-    </row>
-    <row r="20" spans="1:14" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="A20" s="17">
-        <v>1</v>
-      </c>
-      <c r="B20" s="18" t="s">
+      <c r="C19" s="17">
+        <v>2.6</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="F19" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="19">
-        <v>2.6</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="21">
-        <v>1.6</v>
-      </c>
-      <c r="F20" s="22" t="s">
+      <c r="G19" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="N20" s="58" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="16.25" thickTop="1" x14ac:dyDescent="0.75"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="B10:N10"/>
-    <mergeCell ref="B14:N14"/>
-    <mergeCell ref="B16:N16"/>
-    <mergeCell ref="B19:N19"/>
+  <mergeCells count="17">
+    <mergeCell ref="B18:N18"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="A5:N5"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A6:N6"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="B15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="89" orientation="landscape" r:id="rId1"/>
